--- a/ConfigExporter/xlsx/message.xlsx
+++ b/ConfigExporter/xlsx/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3044,6 +3044,78 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>duel_ownership_white_points_sen</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>白方目数: {0}（让先）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>形势白方目数，让先贴0.5目</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>duel_score_confirm_content_sen</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>黑方: {0} 目
+白方: {1} 目（让先，贴 {2}）
+结果: {3}</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>数子确认内容，让先贴0.5目</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>duel_ownership_white_points_handicap</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>白方目数: {0}（让子）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>形势白方目数，让子贴0.5目</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>duel_score_confirm_content_handicap</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>黑方: {0} 目
+白方: {1} 目（让子，贴 {2}）
+结果: {3}</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>数子确认内容，让子贴0.5目</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ConfigExporter/xlsx/message.xlsx
+++ b/ConfigExporter/xlsx/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3116,6 +3116,381 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_wait_title</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>等待对方重连</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>LAN 对局断线等待重连弹窗标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_wait_content</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>连接已中断，正在等待对方重连。
+已等待 {0} 秒。</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>LAN 对局断线等待重连弹窗内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_leave_main_menu</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>退出主菜单</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LAN 对局断线等待重连弹窗按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_restored</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>对方已重连</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>LAN 对局断线重连成功提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_waiting_status</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>正在等待对方重连</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>LAN 房间服务断线等待状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>katago_android_opencl_warmup</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>正在优先预热 Android GPU KataGo 引擎。</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Android OpenCL 优先预热详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>katago_android_opencl_first_init</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>正在初始化 Android GPU KataGo 引擎，首次启动可能需要较长时间。</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Android OpenCL 首次初始化详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>katago_android_opencl_progress_init</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>正在初始化 Android GPU KataGo 引擎，完成后会继续验证 9路、13路、19路棋盘。</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Android OpenCL 初始化进度详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>katago_android_opencl_unavailable_native_warmup</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Android GPU 引擎不可用，正在预热 Android 本地 KataGo 引擎。</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Android OpenCL 不可用转 native/eigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>katago_android_native_warmup</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>正在预热 Android 本地 KataGo 引擎。</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Android native/eigen 预热详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>katago_android_native_verify_board</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Android 本地 KataGo 引擎正在验证 {0}路棋盘。</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Android native/eigen 棋盘验证，0=棋盘路数</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_status</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>AI运行文件准备中...</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Android KataGo 运行文件准备状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_checking</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>正在检查 AI 运行文件。</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Android KataGo 运行文件检查详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_cached</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>AI 运行文件已就绪，正在快速校验。</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Android KataGo 运行文件缓存命中详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_cached_done</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>AI 运行文件检查完成。</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Android KataGo 运行文件缓存校验完成详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_config</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>正在准备 AI 配置文件。</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Android KataGo 配置文件复制详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_model_first</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>首次启动正在复制 AI 模型文件，请稍候。</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Android KataGo 首次模型复制详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_model_progress</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>首次启动正在复制 AI 模型文件，已完成 {0}。</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Android KataGo 首次模型复制进度，0=已复制大小</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>katago_runtime_prepare_done</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>AI 运行文件准备完成。</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Android KataGo 运行文件准备完成详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>lan_room_peer_left</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>对方已离开房间。</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>对方离开房间状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>lan_room_peer_left_title</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>联机已结束</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>对方离开后提示标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>lan_room_peer_left_content</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>对方已离开联机对局，将返回主菜单。</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>对方离开后提示内容</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ConfigExporter/xlsx/message.xlsx
+++ b/ConfigExporter/xlsx/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1940,1554 +1940,1605 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>duel_ownership_black_points</t>
+          <t>duel_pass_consecutive_scoring</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>黑方目数: {0}</t>
+          <t>双方连续虚手，正在数子...</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>形势黑方目数</t>
+          <t>连续虚手提示</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>duel_ownership_white_points</t>
+          <t>duel_ai_suffix</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>白方目数: {0}（贴目后）</t>
+          <t>（AI）</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>形势白方目数</t>
+          <t>AI 行棋后缀</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>duel_ownership_black_calculating</t>
+          <t>duel_pass_notice</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>黑方目数: 计算中...</t>
+          <t>{0}{1}虚手</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>形势黑方计算中</t>
+          <t>虚手提示，0=玩家，1=AI 后缀</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>duel_ownership_white_calculating</t>
+          <t>duel_move_notice</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>白方目数: 计算中...</t>
+          <t>{0}{1}落子 {2}</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>形势白方计算中</t>
+          <t>落子提示，0=玩家，1=AI 后缀，2=坐标</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>duel_pass_consecutive_scoring</t>
+          <t>duel_score_black_win</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>双方连续虚手，正在数子...</t>
+          <t>黑方胜 {0} 目</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>连续虚手提示</t>
+          <t>数子黑胜</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>duel_ai_suffix</t>
+          <t>duel_score_white_win</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>（AI）</t>
+          <t>白方胜 {0} 目</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AI 行棋后缀</t>
+          <t>数子白胜</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>duel_pass_notice</t>
+          <t>duel_score_draw</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{0}{1}虚手</t>
+          <t>双方和棋</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>虚手提示，0=玩家，1=AI 后缀</t>
+          <t>和棋</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>duel_move_notice</t>
+          <t>duel_score_confirm_content</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
-        <is>
-          <t>{0}{1}落子 {2}</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>落子提示，0=玩家，1=AI 后缀，2=坐标</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>duel_score_black_win</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>黑方胜 {0} 目</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>数子黑胜</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>duel_score_white_win</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>白方胜 {0} 目</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>数子白胜</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>duel_score_draw</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>双方和棋</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>和棋</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>duel_score_confirm_content</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
         <is>
           <t>黑方: {0} 目
 白方: {1} 目（含贴目 {2}）
 结果: {3}</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>数子确认内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>duel_hold_time_empty</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>主时间 --</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>主时间空值</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>duel_byoyomi_count_empty</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>剩余读秒 --</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>读秒次数空值</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>duel_byoyomi_time_empty</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>读秒时间 --</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>读秒时间空值</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>duel_hold_time</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>主时间 {0}</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>数子确认内容</t>
+          <t>主时间，0=时间</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>duel_hold_time_empty</t>
+          <t>duel_byoyomi_count</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>主时间 --</t>
+          <t>剩余读秒 {0} 次</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>主时间空值</t>
+          <t>读秒次数，0=次数</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>duel_byoyomi_count_empty</t>
+          <t>duel_byoyomi_time</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>剩余读秒 --</t>
+          <t>读秒时间 {0}</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>读秒次数空值</t>
+          <t>读秒时间，0=时间</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>duel_byoyomi_time_empty</t>
+          <t>duel_game_end_winner</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>读秒时间 --</t>
+          <t>{0}胜出</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>读秒时间空值</t>
+          <t>终局胜者，0=玩家</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>duel_hold_time</t>
+          <t>duel_game_end_timeout</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>主时间 {0}</t>
+          <t>{0}超时判负</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>主时间，0=时间</t>
+          <t>终局超时，0=玩家</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>duel_byoyomi_count</t>
+          <t>duel_game_end_resign</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>剩余读秒 {0} 次</t>
+          <t>{0}认输</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>读秒次数，0=次数</t>
+          <t>终局认输，0=玩家</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>duel_byoyomi_time</t>
+          <t>duel_game_end_score</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>读秒时间 {0}</t>
+          <t>领先 {0} 目</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>读秒时间，0=时间</t>
+          <t>终局数子领先</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>duel_game_end_winner</t>
+          <t>duel_game_end_default</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{0}胜出</t>
+          <t>对局结束</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>终局胜者，0=玩家</t>
+          <t>默认终局原因</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>duel_game_end_timeout</t>
+          <t>duel_ownership_button</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{0}超时判负</t>
+          <t>形势</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>终局超时，0=玩家</t>
+          <t>形势按钮</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>duel_game_end_resign</t>
+          <t>duel_score_confirm_title</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{0}认输</t>
+          <t>确认数子结果</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>终局认输，0=玩家</t>
+          <t>数子结果确认标题</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>duel_game_end_score</t>
+          <t>duel_score_failed_back_to_game</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>领先 {0} 目</t>
+          <t>数子失败，已回到对局</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>终局数子领先</t>
+          <t>数子失败返回对局</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>duel_game_end_default</t>
+          <t>duel_score_not_accepted_title</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>对局结束</t>
+          <t>数子未通过</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>默认终局原因</t>
+          <t>数子未通过标题</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>duel_ownership_button</t>
+          <t>duel_score_retry_later</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>形势</t>
+          <t>数子失败，请稍后重试。</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>形势按钮</t>
+          <t>数子重试提示</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>duel_score_confirm_title</t>
+          <t>duel_save_success</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>确认数子结果</t>
+          <t>对局已保存</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>数子结果确认标题</t>
+          <t>保存成功提示</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>duel_score_failed_back_to_game</t>
+          <t>duel_save_failed</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>数子失败，已回到对局</t>
+          <t>对局保存失败</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>数子失败返回对局</t>
+          <t>保存失败提示</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>duel_score_not_accepted_title</t>
+          <t>duel_scoring_title</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>数子未通过</t>
+          <t>数子中</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>数子未通过标题</t>
+          <t>数子中标题</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>duel_score_retry_later</t>
+          <t>duel_score_opponent_accepted</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>数子失败，请稍后重试。</t>
+          <t>对方已同意数子，正在计算结果。</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>数子重试提示</t>
+          <t>对方同意数子</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>duel_save_success</t>
+          <t>duel_score_request_title</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>对局已保存</t>
+          <t>确认数子</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>保存成功提示</t>
+          <t>数子请求标题</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>duel_save_failed</t>
+          <t>duel_score_request_content</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>对局保存失败</t>
+          <t>对方请求数子，是否同意结束对局并按当前局面计算结果？</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>保存失败提示</t>
+          <t>数子请求内容</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>duel_scoring_title</t>
+          <t>duel_score_accept_request</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>数子中</t>
+          <t>同意数子</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>数子中标题</t>
+          <t>同意数子按钮</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>duel_score_opponent_accepted</t>
+          <t>duel_continue_game</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>对方已同意数子，正在计算结果。</t>
+          <t>继续对局</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>对方同意数子</t>
+          <t>继续对局按钮</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>duel_score_request_title</t>
+          <t>duel_score_accept_result</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>确认数子</t>
+          <t>接受结果</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>数子请求标题</t>
+          <t>接受数子结果按钮</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>duel_score_request_content</t>
+          <t>duel_score_reject_result</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>对方请求数子，是否同意结束对局并按当前局面计算结果？</t>
+          <t>不接受</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>数子请求内容</t>
+          <t>不接受数子结果按钮</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>duel_score_accept_request</t>
+          <t>duel_take_back_title</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>同意数子</t>
+          <t>确认悔棋</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>同意数子按钮</t>
+          <t>悔棋确认标题</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>duel_continue_game</t>
+          <t>duel_take_back_request_content</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>继续对局</t>
+          <t>对方请求悔棋，是否同意回退上一手？</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>继续对局按钮</t>
+          <t>悔棋请求内容</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>duel_score_accept_result</t>
+          <t>duel_take_back_accept</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>接受结果</t>
+          <t>同意悔棋</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>接受数子结果按钮</t>
+          <t>同意悔棋按钮</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>duel_score_reject_result</t>
+          <t>duel_exit_title</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>不接受</t>
+          <t>退出对局</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>不接受数子结果按钮</t>
+          <t>退出对局标题</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>duel_take_back_title</t>
+          <t>duel_exit_content</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>确认悔棋</t>
+          <t>确认退出当前对局？</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>悔棋确认标题</t>
+          <t>退出对局内容</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>duel_take_back_request_content</t>
+          <t>duel_score_wait_title</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>对方请求悔棋，是否同意回退上一手？</t>
+          <t>等待数子确认</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>悔棋请求内容</t>
+          <t>等待数子标题</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>duel_take_back_accept</t>
+          <t>duel_score_wait_content</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>同意悔棋</t>
+          <t>已发送数子请求，正在等待对方同意。</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>同意悔棋按钮</t>
+          <t>等待数子内容</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>duel_exit_title</t>
+          <t>duel_scoring_content</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>退出对局</t>
+          <t>数子中...</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>退出对局标题</t>
+          <t>数子中内容</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>duel_exit_content</t>
+          <t>duel_score_confirm_result</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>确认退出当前对局？</t>
+          <t>确认结果</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>退出对局内容</t>
+          <t>确认数子结果按钮</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>duel_score_wait_title</t>
+          <t>duel_take_back_lan_confirm_content</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>等待数子确认</t>
+          <t>确认向对方请求悔棋？</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>等待数子标题</t>
+          <t>LAN 悔棋提交确认</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>duel_score_wait_content</t>
+          <t>duel_take_back_local_confirm_content</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>已发送数子请求，正在等待对方同意。</t>
+          <t>确认悔棋？</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>等待数子内容</t>
+          <t>本地悔棋确认</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>duel_scoring_content</t>
+          <t>duel_take_back_confirm</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>数子中...</t>
+          <t>确认悔棋</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>数子中内容</t>
+          <t>确认悔棋按钮</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>duel_score_confirm_result</t>
+          <t>duel_resign_title</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>确认结果</t>
+          <t>确认认输</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>确认数子结果按钮</t>
+          <t>认输确认标题</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>duel_take_back_lan_confirm_content</t>
+          <t>duel_resign_content</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>确认向对方请求悔棋？</t>
+          <t>确认{0}认输？</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LAN 悔棋提交确认</t>
+          <t>认输确认内容，0=玩家</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>duel_take_back_local_confirm_content</t>
+          <t>duel_resign_confirm</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>确认悔棋？</t>
+          <t>确认认输</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>本地悔棋确认</t>
+          <t>确认认输按钮</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>duel_take_back_confirm</t>
+          <t>duel_take_back_wait_title</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>确认悔棋</t>
+          <t>等待悔棋确认</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>确认悔棋按钮</t>
+          <t>等待悔棋标题</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>duel_resign_title</t>
+          <t>duel_take_back_wait_content</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>确认认输</t>
+          <t>已发送悔棋请求，正在等待对方同意。</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>认输确认标题</t>
+          <t>等待悔棋内容</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>duel_resign_content</t>
+          <t>duel_take_back_failed</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>确认{0}认输？</t>
+          <t>悔棋失败</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>认输确认内容，0=玩家</t>
+          <t>悔棋失败</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>duel_resign_confirm</t>
+          <t>duel_take_back_opponent_rejected</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>确认认输</t>
+          <t>对方拒绝悔棋</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>确认认输按钮</t>
+          <t>对方拒绝悔棋</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>duel_take_back_wait_title</t>
+          <t>duel_take_back_unavailable</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>等待悔棋确认</t>
+          <t>当前无法悔棋</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>等待悔棋标题</t>
+          <t>无法悔棋</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>duel_take_back_wait_content</t>
+          <t>duel_take_back_scoring_blocked</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>已发送悔棋请求，正在等待对方同意。</t>
+          <t>数子中，暂不能悔棋</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>等待悔棋内容</t>
+          <t>数子阻止悔棋</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>duel_take_back_failed</t>
+          <t>duel_take_back_no_moves</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>悔棋失败</t>
+          <t>无可悔棋的手数</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>悔棋失败</t>
+          <t>无可悔棋手数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>duel_take_back_opponent_rejected</t>
+          <t>duel_take_back_two_moves_success</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>对方拒绝悔棋</t>
+          <t>已回退两手棋</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>对方拒绝悔棋</t>
+          <t>回退两手成功</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>duel_take_back_unavailable</t>
+          <t>duel_take_back_success</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>当前无法悔棋</t>
+          <t>已悔棋</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>无法悔棋</t>
+          <t>悔棋成功</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>duel_take_back_scoring_blocked</t>
+          <t>duel_score_opponent_rejected</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>数子中，暂不能悔棋</t>
+          <t>对方拒绝数子</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>数子阻止悔棋</t>
+          <t>对方拒绝数子</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>duel_take_back_no_moves</t>
+          <t>duel_score_result_rejected</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>无可悔棋的手数</t>
+          <t>有一方不接受结果</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>无可悔棋手数</t>
+          <t>数子结果被拒绝</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>duel_take_back_two_moves_success</t>
+          <t>duel_score_request_unavailable</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>已回退两手棋</t>
+          <t>当前无法请求数子</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>回退两手成功</t>
+          <t>无法请求数子</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>duel_take_back_success</t>
+          <t>duel_score_confirm_content_sen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
-        <is>
-          <t>已悔棋</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>悔棋成功</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>duel_score_opponent_rejected</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>对方拒绝数子</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>对方拒绝数子</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>duel_score_result_rejected</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>有一方不接受结果</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>数子结果被拒绝</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>duel_score_request_unavailable</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>当前无法请求数子</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>无法请求数子</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>duel_ownership_white_points_sen</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>白方目数: {0}（让先）</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>形势白方目数，让先贴0.5目</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>duel_score_confirm_content_sen</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
         <is>
           <t>黑方: {0} 目
 白方: {1} 目（让先，贴 {2}）
 结果: {3}</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>数子确认内容，让先贴0.5目</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>duel_ownership_white_points_handicap</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>白方目数: {0}（让子）</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>形势白方目数，让子贴0.5目</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>duel_score_confirm_content_handicap</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>黑方: {0} 目
 白方: {1} 目（让子，贴 {2}）
 结果: {3}</t>
         </is>
       </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>数子确认内容，让子贴0.5目</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_wait_title</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>等待对方重连</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LAN 对局断线等待重连弹窗标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_wait_content</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>连接已中断，正在等待对方重连。
+已等待 {0} 秒。</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LAN 对局断线等待重连弹窗内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_leave_main_menu</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>退出主菜单</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>LAN 对局断线等待重连弹窗按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_restored</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>对方已重连</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>LAN 对局断线重连成功提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>lan_room_reconnect_waiting_status</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>正在等待对方重连</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>LAN 房间服务断线等待状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>katago_android_opencl_warmup</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>正在优先预热 Android GPU KataGo 引擎。</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>数子确认内容，让子贴0.5目</t>
+          <t>Android OpenCL 优先预热详情</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>lan_room_reconnect_wait_title</t>
+          <t>katago_android_opencl_first_init</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>等待对方重连</t>
+          <t>正在初始化 Android GPU KataGo 引擎，首次启动可能需要较长时间。</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>LAN 对局断线等待重连弹窗标题</t>
+          <t>Android OpenCL 首次初始化详情</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>lan_room_reconnect_wait_content</t>
+          <t>katago_android_opencl_progress_init</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>连接已中断，正在等待对方重连。
-已等待 {0} 秒。</t>
+          <t>正在初始化 Android GPU KataGo 引擎，完成后会继续验证 9路、13路、19路棋盘。</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>LAN 对局断线等待重连弹窗内容</t>
+          <t>Android OpenCL 初始化进度详情</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>lan_room_reconnect_leave_main_menu</t>
+          <t>katago_android_opencl_unavailable_native_warmup</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>退出主菜单</t>
+          <t>Android GPU 引擎不可用，正在预热 Android 本地 KataGo 引擎。</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>LAN 对局断线等待重连弹窗按钮</t>
+          <t>Android OpenCL 不可用转 native/eigen</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>lan_room_reconnect_restored</t>
+          <t>katago_android_native_warmup</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>对方已重连</t>
+          <t>正在预热 Android 本地 KataGo 引擎。</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LAN 对局断线重连成功提示</t>
+          <t>Android native/eigen 预热详情</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>lan_room_reconnect_waiting_status</t>
+          <t>katago_android_native_verify_board</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>正在等待对方重连</t>
+          <t>Android 本地 KataGo 引擎正在验证 {0}路棋盘。</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LAN 房间服务断线等待状态</t>
+          <t>Android native/eigen 棋盘验证，0=棋盘路数</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>katago_android_opencl_warmup</t>
+          <t>katago_runtime_prepare_status</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>正在优先预热 Android GPU KataGo 引擎。</t>
+          <t>AI运行文件准备中...</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Android OpenCL 优先预热详情</t>
+          <t>Android KataGo 运行文件准备状态</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>katago_android_opencl_first_init</t>
+          <t>katago_runtime_prepare_checking</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>正在初始化 Android GPU KataGo 引擎，首次启动可能需要较长时间。</t>
+          <t>正在检查 AI 运行文件。</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Android OpenCL 首次初始化详情</t>
+          <t>Android KataGo 运行文件检查详情</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>katago_android_opencl_progress_init</t>
+          <t>katago_runtime_prepare_cached</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>正在初始化 Android GPU KataGo 引擎，完成后会继续验证 9路、13路、19路棋盘。</t>
+          <t>AI 运行文件已就绪，正在快速校验。</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Android OpenCL 初始化进度详情</t>
+          <t>Android KataGo 运行文件缓存命中详情</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>katago_android_opencl_unavailable_native_warmup</t>
+          <t>katago_runtime_prepare_cached_done</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Android GPU 引擎不可用，正在预热 Android 本地 KataGo 引擎。</t>
+          <t>AI 运行文件检查完成。</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Android OpenCL 不可用转 native/eigen</t>
+          <t>Android KataGo 运行文件缓存校验完成详情</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>katago_android_native_warmup</t>
+          <t>katago_runtime_prepare_config</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>正在预热 Android 本地 KataGo 引擎。</t>
+          <t>正在准备 AI 配置文件。</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Android native/eigen 预热详情</t>
+          <t>Android KataGo 配置文件复制详情</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>katago_android_native_verify_board</t>
+          <t>katago_runtime_prepare_model_first</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Android 本地 KataGo 引擎正在验证 {0}路棋盘。</t>
+          <t>首次启动正在复制 AI 模型文件，请稍候。</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Android native/eigen 棋盘验证，0=棋盘路数</t>
+          <t>Android KataGo 首次模型复制详情</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_status</t>
+          <t>katago_runtime_prepare_model_progress</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AI运行文件准备中...</t>
+          <t>首次启动正在复制 AI 模型文件，已完成 {0}。</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Android KataGo 运行文件准备状态</t>
+          <t>Android KataGo 首次模型复制进度，0=已复制大小</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_checking</t>
+          <t>katago_runtime_prepare_done</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>正在检查 AI 运行文件。</t>
+          <t>AI 运行文件准备完成。</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Android KataGo 运行文件检查详情</t>
+          <t>Android KataGo 运行文件准备完成详情</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_cached</t>
+          <t>lan_room_peer_left</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>AI 运行文件已就绪，正在快速校验。</t>
+          <t>对方已离开房间。</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Android KataGo 运行文件缓存命中详情</t>
+          <t>对方离开房间状态</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_cached_done</t>
+          <t>lan_room_peer_left_title</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>AI 运行文件检查完成。</t>
+          <t>联机已结束</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Android KataGo 运行文件缓存校验完成详情</t>
+          <t>对方离开后提示标题</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_config</t>
+          <t>lan_room_peer_left_content</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>正在准备 AI 配置文件。</t>
+          <t>对方已离开联机对局，将返回主菜单。</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Android KataGo 配置文件复制详情</t>
+          <t>对方离开后提示内容</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_model_first</t>
+          <t>duel_player_black_short</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>首次启动正在复制 AI 模型文件，请稍候。</t>
+          <t>黑</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Android KataGo 首次模型复制详情</t>
+          <t>黑方短显示名</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_model_progress</t>
+          <t>duel_player_white_short</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>首次启动正在复制 AI 模型文件，已完成 {0}。</t>
+          <t>白</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Android KataGo 首次模型复制进度，0=已复制大小</t>
+          <t>白方短显示名</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>katago_runtime_prepare_done</t>
+          <t>duel_ownership_lead_points</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>AI 运行文件准备完成。</t>
+          <t>{0}领先{1}目</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Android KataGo 运行文件准备完成详情</t>
+          <t>形势领先方目数，0=领先方，1=领先目数</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>lan_room_peer_left</t>
+          <t>duel_ownership_lead_even</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>对方已离开房间。</t>
+          <t>双方持平</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>对方离开房间状态</t>
+          <t>形势双方目数持平</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>lan_room_peer_left_title</t>
+          <t>duel_ownership_rule_info</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>联机已结束</t>
+          <t>贴目{0}{1}</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>对方离开后提示标题</t>
+          <t>形势贴目与让子规则信息，0=贴目，1=让先/让子后缀</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>lan_room_peer_left_content</t>
+          <t>duel_ownership_rule_sen_suffix</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>对方已离开联机对局，将返回主菜单。</t>
+          <t>（让先）</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>对方离开后提示内容</t>
+          <t>形势让先后缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>duel_ownership_rule_handicap_suffix</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>（让{0}子）</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>形势让子后缀，0=汉字让子数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>duel_ownership_lead_calculating</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>领先目数: 计算中...</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>形势领先目数计算中</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>duel_ownership_rule_calculating</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>贴目: 计算中...</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>形势贴目规则计算中</t>
         </is>
       </c>
     </row>
